--- a/results/job_matches_2026-07-12.xlsx
+++ b/results/job_matches_2026-07-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,122 +538,122 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>HR AI/ML Engineer II</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Elevate Aviation Group</t>
+          <t>Airbus</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, S3, RDS, Data Factory, Databricks, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9383db09846c90f4</t>
+          <t>https://www.indeed.com/viewjob?jk=7aee672823e50ae6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DevOps Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Kinesis, SQS, Azure, Databricks, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1f3cc801c79c8e7</t>
+          <t>https://www.indeed.com/viewjob?jk=565b08a71b6647d2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HR AI/ML Engineer II</t>
+          <t>Senior Associate - Full Stack Developer - Wealth Management Technology</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Airbus</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Data Factory, Databricks, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, ECS, RDS, Databricks, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aee672823e50ae6</t>
+          <t>https://www.indeed.com/viewjob?jk=8bc74ef26d52ec8e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, Azure, Databricks, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565b08a71b6647d2</t>
+          <t>https://www.indeed.com/viewjob?jk=c380088294d31182</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Associate - Full Stack Developer - Wealth Management Technology</t>
+          <t>Engineer III</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Ross Dress For Less</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,77 +696,77 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, ECS, RDS, Databricks, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bc74ef26d52ec8e</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d894dc94f127d6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Point One Navigation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c380088294d31182</t>
+          <t>https://www.indeed.com/viewjob?jk=7b1b105ae72cedfb</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Engineer III</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ross Dress For Less</t>
+          <t>Point One Navigation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,495 +776,110 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d894dc94f127d6</t>
+          <t>https://www.indeed.com/viewjob?jk=894f57d9a1c304cf</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MTN</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a1e14429b49571c</t>
+          <t>https://www.indeed.com/viewjob?jk=3e6a9633dc466a51</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Data Engineer Intern/Co-op</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b6f9e26dbe6cc6c</t>
+          <t>https://www.indeed.com/viewjob?jk=2bafe231fd54f8af</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer (BI/Fabric)</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LifeWave</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=116ca6571d543788</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Axos Bank</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8c60e10a1b6481c3</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Adidev Technologies Inc</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Santa Monica, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=521e9a8cf4de7cf2</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>ML/AI Engineers</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Adidev Technologies Inc</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ab9861ce9c451ec</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Jr - Mid Level Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Adidev Technologies Inc</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Edison, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5e63c93a86a5d45e</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Adidev Technologies Inc</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=783b7f98787ded08</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Full Stack Product Builder</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Michael Baker International</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Newark, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3934e1788c4103b9</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Point One Navigation</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b1b105ae72cedfb</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Point One Navigation</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=894f57d9a1c304cf</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3e6a9633dc466a51</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Data Engineer Intern/Co-op</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Plymouth Rock Assurance</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2bafe231fd54f8af</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Senior AWS Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Plymouth Rock Assurance</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=1641a10b9bb89296</t>
         </is>

--- a/results/job_matches_2026-07-12.xlsx
+++ b/results/job_matches_2026-07-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineer III</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Ross Dress For Less</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c380088294d31182</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d894dc94f127d6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Engineer III</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ross Dress For Less</t>
+          <t>Point One Navigation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d894dc94f127d6</t>
+          <t>https://www.indeed.com/viewjob?jk=7b1b105ae72cedfb</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b1b105ae72cedfb</t>
+          <t>https://www.indeed.com/viewjob?jk=894f57d9a1c304cf</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Point One Navigation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,112 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=894f57d9a1c304cf</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=3e6a9633dc466a51</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Data Engineer Intern/Co-op</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Plymouth Rock Assurance</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2bafe231fd54f8af</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Senior AWS Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Plymouth Rock Assurance</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1641a10b9bb89296</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-12.xlsx
+++ b/results/job_matches_2026-07-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>HR AI/ML Engineer II</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Airbus</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>13.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Sqoop, HBase, Flume, Spark</t>
+          <t>AWS, S3, RDS, Data Factory, Databricks, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba2f5df91db55ec9</t>
+          <t>https://www.indeed.com/viewjob?jk=7aee672823e50ae6</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RWE</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Delta Live Tables, Cloud Storage, Scala, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Kinesis, SQS, Azure, Databricks, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=275b7a8c06aa4c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=565b08a71b6647d2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HR AI/ML Engineer II</t>
+          <t>Engineer III</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Airbus</t>
+          <t>Ross Dress For Less</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Data Factory, Databricks, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aee672823e50ae6</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d894dc94f127d6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, Azure, Databricks, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -600,181 +600,6 @@
         </is>
       </c>
       <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=565b08a71b6647d2</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Senior Associate - Full Stack Developer - Wealth Management Technology</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>New York Life</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, ECS, RDS, Databricks, Scala</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8bc74ef26d52ec8e</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Engineer III</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Ross Dress For Less</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Dublin, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d894dc94f127d6</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Point One Navigation</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b1b105ae72cedfb</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Point One Navigation</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=894f57d9a1c304cf</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3e6a9633dc466a51</t>
         </is>

--- a/results/job_matches_2026-07-12.xlsx
+++ b/results/job_matches_2026-07-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,33 +573,68 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Oracle OCI Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Lateral Insights</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Great Falls, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ed69d2e91eede4e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>JPMorganChase</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D6" t="n">
         <v>10.4</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3e6a9633dc466a51</t>
         </is>

--- a/results/job_matches_2026-07-12.xlsx
+++ b/results/job_matches_2026-07-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -602,41 +602,6 @@
       <c r="G5" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ed69d2e91eede4e0</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3e6a9633dc466a51</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-12.xlsx
+++ b/results/job_matches_2026-07-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Engineer III</t>
+          <t>Java Technical Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ross Dress For Less</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,50 +556,85 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, ECS, GCP, Kafka, Oracle, MongoDB, Cassandra, NoSQL, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d894dc94f127d6</t>
+          <t>https://www.indeed.com/viewjob?jk=1dd56339bfa2aac5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Engineer III</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ross Dress For Less</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Dublin, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a1d894dc94f127d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Oracle OCI Cloud Engineer</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Lateral Insights</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Great Falls, VA, US USA</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D6" t="n">
         <v>11.8</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ed69d2e91eede4e0</t>
         </is>

--- a/results/job_matches_2026-07-12.xlsx
+++ b/results/job_matches_2026-07-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,52 +468,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HR AI/ML Engineer II</t>
+          <t>Java Technical Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Airbus</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Data Factory, Databricks, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark</t>
+          <t>AWS, ECS, GCP, Kafka, Oracle, MongoDB, Cassandra, NoSQL, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aee672823e50ae6</t>
+          <t>https://www.indeed.com/viewjob?jk=1dd56339bfa2aac5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Engineer III</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ross Dress For Less</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, Azure, Databricks, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,110 +531,40 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565b08a71b6647d2</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d894dc94f127d6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Java Technical Architect</t>
+          <t>Oracle OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Lateral Insights</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Great Falls, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, ECS, GCP, Kafka, Oracle, MongoDB, Cassandra, NoSQL, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1dd56339bfa2aac5</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Engineer III</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Ross Dress For Less</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Dublin, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d894dc94f127d6</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Oracle OCI Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Lateral Insights</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Great Falls, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ed69d2e91eede4e0</t>
         </is>

--- a/results/job_matches_2026-07-12.xlsx
+++ b/results/job_matches_2026-07-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Engineer III</t>
+          <t>Oracle OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ross Dress For Less</t>
+          <t>Lateral Insights</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Great Falls, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -530,41 +530,6 @@
         </is>
       </c>
       <c r="G3" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d894dc94f127d6</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Oracle OCI Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Lateral Insights</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Great Falls, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ed69d2e91eede4e0</t>
         </is>

--- a/results/job_matches_2026-07-12.xlsx
+++ b/results/job_matches_2026-07-12.xlsx
@@ -468,35 +468,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Java Technical Architect</t>
+          <t>Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Digital Strategy LLC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, ECS, GCP, Kafka, Oracle, MongoDB, Cassandra, NoSQL, Jenkins, Maven</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dd56339bfa2aac5</t>
+          <t>https://www.indeed.com/viewjob?jk=cd127ae8715c196f</t>
         </is>
       </c>
     </row>
